--- a/Team-Data/2013-14/11-4-2013-14.xlsx
+++ b/Team-Data/2013-14/11-4-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>-1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF2" t="n">
         <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
         <v>5</v>
@@ -757,13 +824,13 @@
         <v>10</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>9</v>
       </c>
       <c r="AL2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM2" t="n">
         <v>10</v>
@@ -781,13 +848,13 @@
         <v>27</v>
       </c>
       <c r="AR2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
         <v>4</v>
@@ -796,25 +863,25 @@
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
         <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -843,13 +910,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -858,40 +925,40 @@
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="J3" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="K3" t="n">
-        <v>0.455</v>
+        <v>0.449</v>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="M3" t="n">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>0.262</v>
+        <v>0.222</v>
       </c>
       <c r="O3" t="n">
-        <v>18.3</v>
+        <v>19.3</v>
       </c>
       <c r="P3" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.753</v>
+        <v>0.734</v>
       </c>
       <c r="R3" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>29.3</v>
+        <v>29.7</v>
       </c>
       <c r="T3" t="n">
-        <v>38.5</v>
+        <v>40.7</v>
       </c>
       <c r="U3" t="n">
         <v>14.3</v>
@@ -900,34 +967,34 @@
         <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="X3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>87.5</v>
+        <v>87.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>-7.5</v>
+        <v>-7.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
@@ -936,40 +1003,40 @@
         <v>5</v>
       </c>
       <c r="AI3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>12</v>
       </c>
       <c r="AL3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM3" t="n">
         <v>28</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT3" t="n">
         <v>25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>27</v>
       </c>
       <c r="AU3" t="n">
         <v>30</v>
@@ -978,19 +1045,19 @@
         <v>30</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA3" t="n">
         <v>18</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>20</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1170,28 @@
         <v>-8</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
         <v>5</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1133,31 +1200,31 @@
         <v>21</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
         <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
         <v>19</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
         <v>13</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1169,10 +1236,10 @@
         <v>2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -1285,40 +1352,40 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>5</v>
       </c>
       <c r="AI5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
         <v>29</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>30</v>
       </c>
       <c r="AM5" t="n">
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
         <v>6</v>
@@ -1327,7 +1394,7 @@
         <v>30</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
         <v>27</v>
@@ -1336,16 +1403,16 @@
         <v>28</v>
       </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
         <v>3</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
         <v>29</v>
@@ -1357,7 +1424,7 @@
         <v>11</v>
       </c>
       <c r="BB5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC5" t="n">
         <v>29</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>-4.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
         <v>5</v>
@@ -1485,10 +1552,10 @@
         <v>16</v>
       </c>
       <c r="AJ6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>27</v>
@@ -1497,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ6" t="n">
         <v>2</v>
@@ -1512,16 +1579,16 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW6" t="n">
         <v>17</v>
@@ -1530,19 +1597,19 @@
         <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ6" t="n">
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -1571,106 +1638,106 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>33.8</v>
+        <v>32</v>
       </c>
       <c r="J7" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.402</v>
+        <v>0.382</v>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>0.266</v>
+        <v>0.25</v>
       </c>
       <c r="O7" t="n">
-        <v>15.5</v>
+        <v>17.3</v>
       </c>
       <c r="P7" t="n">
-        <v>20.5</v>
+        <v>23.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.732</v>
       </c>
       <c r="R7" t="n">
         <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>33</v>
+        <v>31.3</v>
       </c>
       <c r="T7" t="n">
-        <v>44</v>
+        <v>42.3</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>15.3</v>
       </c>
       <c r="V7" t="n">
-        <v>17.8</v>
+        <v>15.7</v>
       </c>
       <c r="W7" t="n">
         <v>10.3</v>
       </c>
       <c r="X7" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>87.3</v>
+        <v>85.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4</v>
+        <v>-5.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AF7" t="n">
         <v>14</v>
       </c>
       <c r="AG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>14</v>
       </c>
-      <c r="AH7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>10</v>
-      </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
         <v>28</v>
@@ -1682,49 +1749,49 @@
         <v>25</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AT7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV7" t="n">
         <v>13</v>
       </c>
-      <c r="AU7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
       <c r="AW7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AY7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ7" t="n">
         <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BB7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -1831,31 +1898,31 @@
         <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>7</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>8</v>
       </c>
       <c r="AK8" t="n">
         <v>13</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM8" t="n">
         <v>9</v>
@@ -1864,7 +1931,7 @@
         <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP8" t="n">
         <v>4</v>
@@ -1879,25 +1946,25 @@
         <v>18</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
         <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY8" t="n">
         <v>8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA8" t="n">
         <v>7</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -2028,43 +2095,43 @@
         <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ9" t="n">
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM9" t="n">
         <v>24</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="n">
         <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2079,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA9" t="n">
         <v>6</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -2195,28 +2262,28 @@
         <v>6</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK10" t="n">
         <v>7</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>6</v>
       </c>
       <c r="AL10" t="n">
         <v>20</v>
@@ -2225,7 +2292,7 @@
         <v>20</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
         <v>9</v>
@@ -2234,7 +2301,7 @@
         <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
         <v>4</v>
@@ -2243,7 +2310,7 @@
         <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
         <v>17</v>
@@ -2255,13 +2322,13 @@
         <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>8</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -2299,142 +2366,142 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="J11" t="n">
-        <v>82.5</v>
+        <v>79.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.503</v>
+        <v>0.525</v>
       </c>
       <c r="L11" t="n">
-        <v>13.3</v>
+        <v>12.7</v>
       </c>
       <c r="M11" t="n">
-        <v>28.3</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>0.469</v>
+        <v>0.507</v>
       </c>
       <c r="O11" t="n">
-        <v>15.8</v>
+        <v>16.7</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.716</v>
+        <v>0.735</v>
       </c>
       <c r="R11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="S11" t="n">
-        <v>36</v>
+        <v>34.3</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>41.7</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="V11" t="n">
-        <v>20</v>
+        <v>19.3</v>
       </c>
       <c r="W11" t="n">
-        <v>10.3</v>
+        <v>7.7</v>
       </c>
       <c r="X11" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="n">
         <v>3</v>
       </c>
       <c r="Z11" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="AA11" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
         <v>22</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>112</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AX11" t="n">
         <v>5</v>
@@ -2446,13 +2513,13 @@
         <v>27</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB11" t="n">
         <v>2</v>
       </c>
       <c r="BC11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -2481,118 +2548,118 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>36.3</v>
+        <v>34.7</v>
       </c>
       <c r="J12" t="n">
-        <v>74.5</v>
+        <v>72</v>
       </c>
       <c r="K12" t="n">
-        <v>0.487</v>
+        <v>0.481</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>25.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.356</v>
+        <v>0.382</v>
       </c>
       <c r="O12" t="n">
-        <v>26.3</v>
+        <v>25.3</v>
       </c>
       <c r="P12" t="n">
-        <v>38.3</v>
+        <v>36.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>35.5</v>
+        <v>36.3</v>
       </c>
       <c r="T12" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="U12" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="V12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W12" t="n">
         <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.3</v>
+        <v>19.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>28</v>
+        <v>27.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>107.8</v>
+        <v>104.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>10.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH12" t="n">
         <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2604,37 +2671,37 @@
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
         <v>23</v>
       </c>
       <c r="AV12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
         <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2756,22 +2823,22 @@
         <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK13" t="n">
         <v>14</v>
       </c>
       <c r="AL13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN13" t="n">
         <v>8</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>7</v>
       </c>
       <c r="AO13" t="n">
         <v>6</v>
@@ -2783,13 +2850,13 @@
         <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
         <v>18</v>
@@ -2804,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
         <v>1</v>
@@ -2816,7 +2883,7 @@
         <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -2845,115 +2912,115 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>41.8</v>
+        <v>39.3</v>
       </c>
       <c r="J14" t="n">
-        <v>83</v>
+        <v>79.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.503</v>
+        <v>0.496</v>
       </c>
       <c r="L14" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>27.8</v>
+        <v>24.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="O14" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="P14" t="n">
-        <v>33.8</v>
+        <v>35.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.726</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="S14" t="n">
         <v>29</v>
       </c>
       <c r="T14" t="n">
-        <v>40.3</v>
+        <v>41</v>
       </c>
       <c r="U14" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>10</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AA14" t="n">
         <v>28.3</v>
       </c>
-      <c r="V14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="X14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
+        <v>113</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD14" t="n">
         <v>4</v>
       </c>
-      <c r="Z14" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>119</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,43 +3029,43 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
         <v>24</v>
       </c>
       <c r="AT14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>30</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
@@ -3120,7 +3187,7 @@
         <v>5</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
         <v>3</v>
@@ -3129,10 +3196,10 @@
         <v>24</v>
       </c>
       <c r="AL15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM15" t="n">
         <v>6</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>8</v>
       </c>
       <c r="AN15" t="n">
         <v>9</v>
@@ -3141,13 +3208,13 @@
         <v>17</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>1</v>
@@ -3159,28 +3226,28 @@
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
         <v>26</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -3209,115 +3276,115 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H16" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="I16" t="n">
-        <v>38</v>
+        <v>38.7</v>
       </c>
       <c r="J16" t="n">
-        <v>82.8</v>
+        <v>85.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.459</v>
+        <v>0.451</v>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
         <v>18.3</v>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.785</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="S16" t="n">
-        <v>31.5</v>
+        <v>33</v>
       </c>
       <c r="T16" t="n">
-        <v>42.3</v>
+        <v>44.3</v>
       </c>
       <c r="U16" t="n">
         <v>23</v>
       </c>
       <c r="V16" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="W16" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="AA16" t="n">
         <v>21.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.8</v>
+        <v>101.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>-2.3</v>
+        <v>-5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AK16" t="n">
         <v>11</v>
       </c>
       <c r="AL16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>15</v>
@@ -3326,43 +3393,43 @@
         <v>19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV16" t="n">
         <v>17</v>
       </c>
       <c r="AW16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY16" t="n">
         <v>18</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>18</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF17" t="n">
         <v>14</v>
@@ -3487,16 +3554,16 @@
         <v>11</v>
       </c>
       <c r="AJ17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL17" t="n">
         <v>2</v>
       </c>
       <c r="AM17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
         <v>3</v>
@@ -3505,10 +3572,10 @@
         <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,22 +3587,22 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
         <v>2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>5</v>
@@ -3544,7 +3611,7 @@
         <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3718,25 @@
         <v>-2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
         <v>5</v>
       </c>
       <c r="AI18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
         <v>15</v>
@@ -3681,10 +3748,10 @@
         <v>26</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>23</v>
@@ -3705,13 +3772,13 @@
         <v>16</v>
       </c>
       <c r="AV18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY18" t="n">
         <v>13</v>
@@ -3720,13 +3787,13 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
         <v>24</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -3755,118 +3822,118 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="I19" t="n">
-        <v>36</v>
+        <v>36.7</v>
       </c>
       <c r="J19" t="n">
-        <v>87.5</v>
+        <v>85.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.411</v>
+        <v>0.43</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N19" t="n">
-        <v>0.31</v>
+        <v>0.361</v>
       </c>
       <c r="O19" t="n">
-        <v>25.5</v>
+        <v>27.7</v>
       </c>
       <c r="P19" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R19" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="T19" t="n">
-        <v>44.8</v>
+        <v>45.3</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="V19" t="n">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="W19" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="X19" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>26.8</v>
+        <v>27.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.3</v>
+        <v>109.7</v>
       </c>
       <c r="AC19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM19" t="n">
         <v>8</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI19" t="n">
+      <c r="AN19" t="n">
         <v>16</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>21</v>
-      </c>
       <c r="AO19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3875,40 +3942,40 @@
         <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>-1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH20" t="n">
         <v>5</v>
@@ -4033,7 +4100,7 @@
         <v>22</v>
       </c>
       <c r="AJ20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK20" t="n">
         <v>25</v>
@@ -4045,13 +4112,13 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>7</v>
       </c>
       <c r="AP20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
         <v>5</v>
@@ -4063,7 +4130,7 @@
         <v>21</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>15</v>
@@ -4081,7 +4148,7 @@
         <v>27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA20" t="n">
         <v>25</v>
@@ -4090,7 +4157,7 @@
         <v>17</v>
       </c>
       <c r="BC20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -4197,25 +4264,25 @@
         <v>-1</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH21" t="n">
         <v>5</v>
       </c>
       <c r="AI21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
         <v>16</v>
@@ -4245,19 +4312,19 @@
         <v>19</v>
       </c>
       <c r="AT21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU21" t="n">
         <v>20</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
         <v>3</v>
       </c>
       <c r="AX21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
         <v>1</v>
@@ -4272,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="BC21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -4379,40 +4446,40 @@
         <v>-3</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH22" t="n">
         <v>5</v>
       </c>
       <c r="AI22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK22" t="n">
         <v>28</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>29</v>
       </c>
       <c r="AL22" t="n">
         <v>25</v>
       </c>
       <c r="AM22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN22" t="n">
         <v>30</v>
       </c>
       <c r="AO22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP22" t="n">
         <v>7</v>
@@ -4421,13 +4488,13 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU22" t="n">
         <v>29</v>
@@ -4439,13 +4506,13 @@
         <v>10</v>
       </c>
       <c r="AX22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY22" t="n">
         <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
         <v>9</v>
@@ -4454,7 +4521,7 @@
         <v>17</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF23" t="n">
         <v>14</v>
@@ -4573,7 +4640,7 @@
         <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI23" t="n">
         <v>4</v>
@@ -4585,7 +4652,7 @@
         <v>8</v>
       </c>
       <c r="AL23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM23" t="n">
         <v>17</v>
@@ -4594,31 +4661,31 @@
         <v>5</v>
       </c>
       <c r="AO23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
         <v>2</v>
       </c>
       <c r="AT23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
         <v>19</v>
       </c>
       <c r="AV23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -4627,16 +4694,16 @@
         <v>30</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -4665,160 +4732,160 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>41</v>
+        <v>44.3</v>
       </c>
       <c r="J24" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.471</v>
+        <v>0.512</v>
       </c>
       <c r="L24" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>22.8</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
-        <v>0.33</v>
+        <v>0.379</v>
       </c>
       <c r="O24" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="P24" t="n">
-        <v>23.3</v>
+        <v>18.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.667</v>
+        <v>0.696</v>
       </c>
       <c r="R24" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="S24" t="n">
-        <v>34</v>
+        <v>32.7</v>
       </c>
       <c r="T24" t="n">
-        <v>44.3</v>
+        <v>41.7</v>
       </c>
       <c r="U24" t="n">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
       <c r="V24" t="n">
-        <v>19</v>
+        <v>17.3</v>
       </c>
       <c r="W24" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="X24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD24" t="n">
         <v>4</v>
       </c>
-      <c r="Y24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>105</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1</v>
-      </c>
       <c r="AE24" t="n">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK24" t="n">
         <v>2</v>
       </c>
-      <c r="AG24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI24" t="n">
+      <c r="AL24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>4</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="BA24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC24" t="n">
         <v>7</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>17</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -4925,40 +4992,40 @@
         <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH25" t="n">
         <v>5</v>
       </c>
       <c r="AI25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK25" t="n">
         <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN25" t="n">
         <v>22</v>
       </c>
       <c r="AO25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP25" t="n">
         <v>23</v>
@@ -4979,13 +5046,13 @@
         <v>22</v>
       </c>
       <c r="AV25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -4994,7 +5061,7 @@
         <v>11</v>
       </c>
       <c r="BA25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -5107,22 +5174,22 @@
         <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ26" t="n">
         <v>2</v>
@@ -5131,34 +5198,34 @@
         <v>10</v>
       </c>
       <c r="AL26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
         <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
         <v>2</v>
@@ -5167,22 +5234,22 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -5289,28 +5356,28 @@
         <v>-6</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF27" t="n">
         <v>14</v>
       </c>
       <c r="AG27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH27" t="n">
         <v>5</v>
       </c>
       <c r="AI27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK27" t="n">
         <v>26</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>27</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
@@ -5319,7 +5386,7 @@
         <v>16</v>
       </c>
       <c r="AN27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
         <v>9</v>
@@ -5340,7 +5407,7 @@
         <v>23</v>
       </c>
       <c r="AU27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
@@ -5349,7 +5416,7 @@
         <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -5471,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH28" t="n">
         <v>5</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
         <v>15</v>
@@ -5519,10 +5586,10 @@
         <v>14</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>3</v>
@@ -5531,7 +5598,7 @@
         <v>27</v>
       </c>
       <c r="AX28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AY28" t="n">
         <v>20</v>
@@ -5546,7 +5613,7 @@
         <v>14</v>
       </c>
       <c r="BC28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -5653,25 +5720,25 @@
         <v>2</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
       </c>
       <c r="AI29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK29" t="n">
         <v>18</v>
@@ -5686,10 +5753,10 @@
         <v>24</v>
       </c>
       <c r="AO29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ29" t="n">
         <v>29</v>
@@ -5698,16 +5765,16 @@
         <v>1</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT29" t="n">
         <v>1</v>
       </c>
       <c r="AU29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW29" t="n">
         <v>23</v>
@@ -5728,7 +5795,7 @@
         <v>17</v>
       </c>
       <c r="BC29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
         <v>27</v>
@@ -5850,13 +5917,13 @@
         <v>5</v>
       </c>
       <c r="AI30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL30" t="n">
         <v>25</v>
@@ -5865,7 +5932,7 @@
         <v>19</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>13</v>
@@ -5874,7 +5941,7 @@
         <v>9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR30" t="n">
         <v>1</v>
@@ -5889,7 +5956,7 @@
         <v>21</v>
       </c>
       <c r="AV30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW30" t="n">
         <v>24</v>
@@ -5898,7 +5965,7 @@
         <v>21</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>22</v>
@@ -5910,7 +5977,7 @@
         <v>26</v>
       </c>
       <c r="BC30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
         <v>27</v>
@@ -6035,28 +6102,28 @@
         <v>12</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>17</v>
       </c>
       <c r="AL31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="n">
         <v>12</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
         <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
         <v>3</v>
@@ -6065,28 +6132,28 @@
         <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU31" t="n">
         <v>13</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ31" t="n">
         <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-4-2013-14</t>
+          <t>2013-11-04</t>
         </is>
       </c>
     </row>
